--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LEYMA CORUÑA.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LEYMA CORUÑA.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>13.618</v>
+        <v>11.0363</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4788</v>
+        <v>8.9763</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1391</v>
+        <v>2.0599</v>
       </c>
       <c r="G2" t="n">
         <v>2.9102</v>
@@ -610,13 +610,13 @@
         <v>5.2865</v>
       </c>
       <c r="S2" t="n">
-        <v>7.2805</v>
+        <v>4.6987</v>
       </c>
       <c r="T2" t="n">
-        <v>5.6173</v>
+        <v>3.1147</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6632</v>
+        <v>1.584</v>
       </c>
       <c r="V2" t="n">
         <v>2.9867</v>
@@ -643,13 +643,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>11.1323</v>
+        <v>10.4476</v>
       </c>
       <c r="E3" t="n">
-        <v>6.459300000000001</v>
+        <v>6.182899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6729</v>
+        <v>4.264699999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.3278999999999999</v>
@@ -688,13 +688,13 @@
         <v>3.9649</v>
       </c>
       <c r="S3" t="n">
-        <v>4.0688</v>
+        <v>3.3841</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8399</v>
+        <v>1.5635</v>
       </c>
       <c r="U3" t="n">
-        <v>2.229</v>
+        <v>1.8207</v>
       </c>
       <c r="V3" t="n">
         <v>5.414</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.8489</v>
+        <v>9.8565</v>
       </c>
       <c r="E4" t="n">
-        <v>4.955299999999999</v>
+        <v>6.788</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8935</v>
+        <v>3.0685</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3842999999999996</v>
+        <v>1.5133</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8286</v>
+        <v>0.2957</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4442</v>
+        <v>1.2175</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9115</v>
+        <v>4.490399999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6973</v>
+        <v>0.8768000000000002</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7858999999999998</v>
+        <v>3.6136</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5272</v>
+        <v>-2.9772</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1310000000000001</v>
+        <v>-0.581</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6583</v>
+        <v>-2.3961</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6258</v>
+        <v>2.8636</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2203</v>
+        <v>-5.7271</v>
       </c>
       <c r="R4" t="n">
-        <v>4.846</v>
+        <v>8.5906</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0899</v>
+        <v>0.4445</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9602</v>
+        <v>0.5667</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1297</v>
+        <v>-0.1223</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7489000000000001</v>
+        <v>5.0351</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3039</v>
+        <v>7.4579</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5549999999999999</v>
+        <v>-2.4228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7.5808</v>
+        <v>8.3452</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9978</v>
+        <v>3.3176</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5831</v>
+        <v>5.0276</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5133</v>
+        <v>5.7213</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2957</v>
+        <v>4.488799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2175</v>
+        <v>1.2326</v>
       </c>
       <c r="J5" t="n">
-        <v>4.490399999999999</v>
+        <v>7.2719</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8768000000000002</v>
+        <v>3.7564</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6136</v>
+        <v>3.5155</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9772</v>
+        <v>-1.5507</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.581</v>
+        <v>0.7325</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3961</v>
+        <v>-2.2833</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8636</v>
+        <v>2.8637</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.7271</v>
+        <v>-3.5244</v>
       </c>
       <c r="R5" t="n">
-        <v>8.5906</v>
+        <v>6.3879</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8313</v>
+        <v>-0.05900000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2236</v>
+        <v>-0.43</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6075999999999999</v>
+        <v>0.3709</v>
       </c>
       <c r="V5" t="n">
-        <v>5.0351</v>
+        <v>-0.1805000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4579</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4228</v>
+        <v>-0.1805000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9363</v>
+        <v>7.0134</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5382</v>
+        <v>3.9229</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3982</v>
+        <v>3.0907</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7213</v>
+        <v>0.3842999999999996</v>
       </c>
       <c r="H6" t="n">
-        <v>4.488799999999999</v>
+        <v>2.8286</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2326</v>
+        <v>-2.4442</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2719</v>
+        <v>1.9115</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7564</v>
+        <v>2.6973</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5155</v>
+        <v>-0.7858999999999998</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5507</v>
+        <v>-1.5272</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7325</v>
+        <v>0.1310000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2833</v>
+        <v>-1.6583</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8637</v>
+        <v>4.6258</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.5244</v>
+        <v>-0.2203</v>
       </c>
       <c r="R6" t="n">
-        <v>6.3879</v>
+        <v>4.846</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.4678</v>
+        <v>1.2545</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.2092</v>
+        <v>0.9277</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2586</v>
+        <v>0.3268</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1805000000000001</v>
+        <v>0.7489000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.3039</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1805000000000001</v>
+        <v>-0.5549999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.126999999999999</v>
+        <v>0.2388000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>4.154999999999999</v>
+        <v>-2.0149</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0279999999999998</v>
+        <v>2.2537</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4121</v>
+        <v>-0.9615</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2385</v>
+        <v>-5.1938</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1736</v>
+        <v>4.2323</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9405999999999998</v>
+        <v>-1.6333</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5645</v>
+        <v>-5.4259</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6238999999999999</v>
+        <v>3.7925</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4714</v>
+        <v>0.6719000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>0.326</v>
+        <v>0.232</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7974</v>
+        <v>0.4398</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2203999999999999</v>
+        <v>-3.9648</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.6257</v>
+        <v>-7.4892</v>
       </c>
       <c r="R7" t="n">
-        <v>4.8461</v>
+        <v>3.5243</v>
       </c>
       <c r="S7" t="n">
-        <v>9.7508</v>
+        <v>0.5045999999999998</v>
       </c>
       <c r="T7" t="n">
-        <v>7.3076</v>
+        <v>1.1431</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4431</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4318</v>
+        <v>4.6607</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4138</v>
+        <v>5.9646</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.8457</v>
+        <v>-1.3039</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0383</v>
+        <v>-0.7736999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0161</v>
+        <v>0.1934</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9779</v>
+        <v>-0.9671000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9615</v>
+        <v>-3.4121</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.1938</v>
+        <v>-1.2385</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2323</v>
+        <v>-2.1736</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6333</v>
+        <v>-0.9405999999999998</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.4259</v>
+        <v>-1.5645</v>
       </c>
       <c r="L8" t="n">
-        <v>3.7925</v>
+        <v>0.6238999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6719000000000002</v>
+        <v>-2.4714</v>
       </c>
       <c r="N8" t="n">
-        <v>0.232</v>
+        <v>0.326</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4398</v>
+        <v>-2.7974</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.9648</v>
+        <v>0.2203999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.4892</v>
+        <v>-4.6257</v>
       </c>
       <c r="R8" t="n">
-        <v>3.5243</v>
+        <v>4.8461</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7725</v>
+        <v>4.8499</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1418</v>
+        <v>3.346</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.9143</v>
+        <v>1.504</v>
       </c>
       <c r="V8" t="n">
-        <v>4.6607</v>
+        <v>-2.4318</v>
       </c>
       <c r="W8" t="n">
-        <v>5.9646</v>
+        <v>2.4138</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3039</v>
+        <v>-4.8457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1136</v>
+        <v>-0.8717999999999995</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9456</v>
+        <v>3.5651</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1682</v>
+        <v>-4.436900000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.08099999999999996</v>
+        <v>2.1877</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4756</v>
+        <v>3.962300000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5566</v>
+        <v>-1.7746</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.07410000000000005</v>
+        <v>3.1961</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5931000000000001</v>
+        <v>3.8244</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6672</v>
+        <v>-0.6282000000000005</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.006899999999999962</v>
+        <v>-1.0084</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1176</v>
+        <v>0.1379000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1106</v>
+        <v>-1.1464</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9825</v>
+        <v>-1.542</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4231</v>
+        <v>-5.0663</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4406</v>
+        <v>3.5244</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0502</v>
+        <v>0.3414000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4484</v>
+        <v>0.2152</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6018</v>
+        <v>0.1261</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8589</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>5.2201</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-7.0789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2503</v>
+        <v>-2.8235</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3262</v>
+        <v>-2.8284</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9242</v>
+        <v>0.004799999999999961</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3397</v>
+        <v>-0.08099999999999996</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8994</v>
+        <v>0.4756</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.44</v>
+        <v>-0.5566</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6285000000000001</v>
+        <v>-0.07410000000000005</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0463</v>
+        <v>0.5931000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4176</v>
+        <v>-0.6672</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.711</v>
+        <v>-0.006899999999999962</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8532999999999998</v>
+        <v>-0.1176</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8579</v>
+        <v>0.1106</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.881</v>
+        <v>-1.9825</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.846</v>
+        <v>-2.4231</v>
       </c>
       <c r="R10" t="n">
-        <v>3.9649</v>
+        <v>0.4406</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6004</v>
+        <v>-0.76</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4261</v>
+        <v>-0.3312</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1742</v>
+        <v>-0.4288</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3700000000000001</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7222</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.3523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.083</v>
+        <v>-3.3157</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5719999999999994</v>
+        <v>-6.9084</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.6551</v>
+        <v>3.5925</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1877</v>
+        <v>-0.522</v>
       </c>
       <c r="H11" t="n">
-        <v>3.962300000000001</v>
+        <v>-3.4066</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7746</v>
+        <v>2.8844</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1961</v>
+        <v>3.0748</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8244</v>
+        <v>-2.7635</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6282000000000005</v>
+        <v>5.8382</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0084</v>
+        <v>-3.5968</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1379000000000001</v>
+        <v>-0.6432</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1464</v>
+        <v>-2.9536</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.542</v>
+        <v>-2.8635</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.0663</v>
+        <v>-11.4542</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5244</v>
+        <v>8.5906</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.8699</v>
+        <v>0.2594000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.778</v>
+        <v>-0.3876999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0919</v>
+        <v>0.6471</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8589</v>
+        <v>-0.1895000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>5.2201</v>
+        <v>1.8589</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.0789</v>
+        <v>-2.0484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7816</v>
+        <v>-3.8104</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.987400000000001</v>
+        <v>-2.0712</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2056</v>
+        <v>-1.7391</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.522</v>
+        <v>-3.3397</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4066</v>
+        <v>-1.8994</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8844</v>
+        <v>-1.44</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0748</v>
+        <v>-0.6285000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7635</v>
+        <v>-1.0463</v>
       </c>
       <c r="L12" t="n">
-        <v>5.8382</v>
+        <v>0.4176</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5968</v>
+        <v>-2.711</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6432</v>
+        <v>-0.8532999999999998</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9536</v>
+        <v>-1.8579</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8635</v>
+        <v>-0.881</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.4542</v>
+        <v>-4.846</v>
       </c>
       <c r="R12" t="n">
-        <v>8.5906</v>
+        <v>3.9649</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2066</v>
+        <v>0.04020000000000006</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4668</v>
+        <v>-0.319</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2602</v>
+        <v>0.3592</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1895000000000001</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8589</v>
+        <v>3.7222</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.0484</v>
+        <v>-3.3523</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>29.9765</v>
+        <v>35.34270000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>16.8811</v>
+        <v>19.1233</v>
       </c>
       <c r="F13" t="n">
-        <v>13.0948</v>
+        <v>16.2193</v>
       </c>
       <c r="G13" t="n">
-        <v>4.728399999999999</v>
+        <v>4.7284</v>
       </c>
       <c r="H13" t="n">
         <v>5.509600000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7808999999999999</v>
+        <v>-0.7808999999999993</v>
       </c>
       <c r="J13" t="n">
         <v>22.335</v>
@@ -1459,7 +1459,7 @@
         <v>-16.1384</v>
       </c>
       <c r="P13" t="n">
-        <v>1.102099999999998</v>
+        <v>1.102099999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-52.8656</v>
@@ -1468,13 +1468,13 @@
         <v>53.96680000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>9.592099999999997</v>
+        <v>14.9583</v>
       </c>
       <c r="T13" t="n">
-        <v>7.166899999999999</v>
+        <v>9.408999999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4252</v>
+        <v>5.549100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>14.5547</v>
